--- a/survey_templates/049_zoo_member_experience_survey--survey_templates.xlsx
+++ b/survey_templates/049_zoo_member_experience_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_1_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,56 +552,64 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Rate your overall experience</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Scale - 1 (very dissatisfied) to 5 (very satisfied)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_3_rate_reason</t>
+          <t>zoo_member_experience_survey_3_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rate_reason</t>
+          <t>How satisfied are you with your visit?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction</t>
+          <t>zoo_member_experience_survey_4_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>satisfaction</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Email (optional)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter your email address</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,10 +629,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Additional feedback</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tell us about your experience</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,66 +646,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_6_email</t>
+          <t>zoo_member_experience_survey_6_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Visit Time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HH -MM 24h format</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_7_phone</t>
+          <t>zoo_member_experience_survey_7_category</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_8_notes</t>
+          <t>zoo_member_experience_survey_8_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Share your thoughts</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,40 +723,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_9_time</t>
+          <t>zoo_member_experience_survey_9_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Do you agree with the following statement?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_10_date</t>
+          <t>zoo_member_experience_survey_10_disagree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Do you disagree with the following statement?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_11_category</t>
+          <t>zoo_member_experience_survey_11_agree_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Zoo Member Experience Survey 11 Agree 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +792,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_12_comments</t>
+          <t>zoo_member_experience_survey_12_disagree_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Zoo Member Experience Survey 12 Disagree 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_13_category_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_14_comments_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_15_agree</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_16_disagree_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>disagree_2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_17_agree_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>agree_2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_18_disagree_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_19_neutral</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_20_disagree_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>disagree_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_21_agree_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>agree_3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_22_disagree_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>disagree_3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_23_agree_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>agree_4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_24_disagree_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>disagree_4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_25_agree_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>agree_5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +823,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +851,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction_choices</t>
+          <t>zoo_member_experience_survey_3_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +861,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction_choices</t>
+          <t>zoo_member_experience_survey_3_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,31 +878,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction_choices</t>
+          <t>zoo_member_experience_survey_3_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>neither_satisfied_nor_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>neither_satisfied_nor_dissatisfied</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction_choices</t>
+          <t>zoo_member_experience_survey_3_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +912,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_4_satisfaction_choices</t>
+          <t>zoo_member_experience_survey_3_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,109 +936,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_11_category_choices</t>
+          <t>zoo_member_experience_survey_7_category_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_11_category_choices</t>
+          <t>zoo_member_experience_survey_7_category_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_11_category_choices</t>
+          <t>zoo_member_experience_survey_7_category_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_13_category_2_choices</t>
+          <t>zoo_member_experience_survey_9_agree_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>category1</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_13_category_2_choices</t>
+          <t>zoo_member_experience_survey_9_agree_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>category2</t>
+          <t>disagree</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_13_category_2_choices</t>
+          <t>zoo_member_experience_survey_9_agree_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>category3</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_15_agree_choices</t>
+          <t>zoo_member_experience_survey_10_disagree_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1055,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_15_agree_choices</t>
+          <t>zoo_member_experience_survey_10_disagree_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1072,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_15_agree_choices</t>
+          <t>zoo_member_experience_survey_10_disagree_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1089,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_16_disagree_2_choices</t>
+          <t>zoo_member_experience_survey_11_agree_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1106,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_16_disagree_2_choices</t>
+          <t>zoo_member_experience_survey_11_agree_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1123,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_16_disagree_2_choices</t>
+          <t>zoo_member_experience_survey_11_agree_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1140,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_17_agree_2_choices</t>
+          <t>zoo_member_experience_survey_12_disagree_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1157,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_17_agree_2_choices</t>
+          <t>zoo_member_experience_survey_12_disagree_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1174,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zoo_member_experience_survey_17_agree_2_choices</t>
+          <t>zoo_member_experience_survey_12_disagree_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1458,414 +1183,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_18_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_18_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_18_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_19_neutral_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_19_neutral_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_19_neutral_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_20_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_20_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_20_disagree_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_21_agree_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_21_agree_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_21_agree_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_22_disagree_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_22_disagree_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_22_disagree_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_23_agree_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_23_agree_4_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_23_agree_4_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_24_disagree_4_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_24_disagree_4_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_24_disagree_4_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_25_agree_5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_25_agree_5_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>zoo_member_experience_survey_25_agree_5_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>neutral</t>
         </is>
